--- a/etf_holdings/2026-09-01_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-09-01_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,16 +451,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>川湖科技</t>
+          <t>國巨股份</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -474,23 +474,23 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>00991A(-10,000)、00993A(-1,000)</t>
+          <t>00991A(-200,000)、00403A(-1,785,000)、00993A(-2,000)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>國巨股份</t>
+          <t>台灣積體</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -504,23 +504,23 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00991A(-200,000)、00993A(-2,000)</t>
+          <t>00991A(-200,000)、00403A(-200,000)、00993A(-3,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>台灣積體</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -534,19 +534,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>00991A(-200,000)、00993A(-3,000)</t>
+          <t>00991A(-100,000)、00982A(-100,000)、00993A(-1,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>川湖科技</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -564,19 +564,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>00991A(-100,000)、00993A(-1,000)</t>
+          <t>00991A(-10,000)、00993A(-1,000)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>台光電子</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -584,29 +584,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00991A(新納入)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>00991A(-20,000)、00993A(-1,000)</t>
+          <t>00993A(-7,000)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>南亞科技</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -624,19 +624,19 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>00991A(-200,000)、00993A(-5,000)</t>
+          <t>00403A(-1,500,000)、00993A(-3,000)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>聯發科技</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -654,19 +654,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>00991A(-100,000)、00993A(-1,000)</t>
+          <t>00403A(-5,000,000)、00993A(-9,000)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>台光電子</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -674,29 +674,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>00991A(100,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>00993A(-1,000)</t>
+          <t>00991A(-20,000)、00993A(-1,000)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>台燿科技</t>
+          <t>南亞科技</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -714,19 +714,19 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>00991A(-400,000)、00993A(-2,000)</t>
+          <t>00991A(-200,000)、00993A(-5,000)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>緯穎科技</t>
+          <t>聯發科技</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -744,37 +744,217 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>00991A(-20,000)、00993A(-1,000)</t>
+          <t>00991A(-100,000)、00993A(-1,000)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>聯亞光電</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>00991A(100,000)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>00993A(-1,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>00403A(-1,000,000)、00993A(-2,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>台燿科技</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>00991A(-400,000)、00993A(-2,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>00981A(53,000)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>00993A(-1,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>緯穎科技</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>00991A(-20,000)、00993A(-1,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>7769</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>鴻勁精密</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>00991A(-60,000)、00993A(-1,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>00992A(329,000)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>00993A(-2,000)</t>
         </is>
       </c>
     </row>
